--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261008.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261008.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>122,705</t>
+          <t>19,037</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>19,037</t>
+          <t>122,705</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
